--- a/Fishing.xlsx
+++ b/Fishing.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seeva\PycharmProjects\FishingAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290826AD-FCA2-430D-9F65-1D17CD25CB7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51DC483-ACB0-45EB-8D4C-21FCA83C2331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{82173828-75BE-405C-8870-0257E5D1189B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="43">
   <si>
     <t>Squid</t>
   </si>
@@ -83,9 +83,6 @@
     <t>Thornfish</t>
   </si>
   <si>
-    <t>Snapper Salmon</t>
-  </si>
-  <si>
     <t>Mid</t>
   </si>
   <si>
@@ -132,6 +129,42 @@
   </si>
   <si>
     <t>Coachwhip Trevally</t>
+  </si>
+  <si>
+    <t>Javelin Grunter</t>
+  </si>
+  <si>
+    <t>Dusky kob</t>
+  </si>
+  <si>
+    <t>Russels Snapper</t>
+  </si>
+  <si>
+    <t>Yellow edged pufferfish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blacktip trevally </t>
+  </si>
+  <si>
+    <t>Blacktail</t>
+  </si>
+  <si>
+    <t>Backtail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid </t>
+  </si>
+  <si>
+    <t>Earthworm lure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Russels Snapper </t>
+  </si>
+  <si>
+    <t>Cape Moony</t>
+  </si>
+  <si>
+    <t>Prison Goby</t>
   </si>
 </sst>
 </file>
@@ -193,8 +226,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2393E883-3052-420D-BBA0-FE3DDC8041F9}" name="Table2" displayName="Table2" ref="A1:C49" totalsRowShown="0">
-  <autoFilter ref="A1:C49" xr:uid="{2393E883-3052-420D-BBA0-FE3DDC8041F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2393E883-3052-420D-BBA0-FE3DDC8041F9}" name="Table2" displayName="Table2" ref="A1:C114" totalsRowShown="0">
+  <autoFilter ref="A1:C114" xr:uid="{2393E883-3052-420D-BBA0-FE3DDC8041F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C18">
     <sortCondition ref="A1:A18"/>
   </sortState>
@@ -524,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{107E5C92-4114-4EFB-8BD8-377966D9CC54}">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
@@ -542,18 +575,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
         <v>20</v>
-      </c>
-      <c r="C1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -567,7 +600,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
         <v>0</v>
@@ -578,7 +611,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
         <v>0</v>
@@ -600,7 +633,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
         <v>0</v>
@@ -641,7 +674,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
@@ -666,7 +699,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
         <v>0</v>
@@ -685,7 +718,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
         <v>2</v>
@@ -743,7 +776,7 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
         <v>0</v>
@@ -754,7 +787,7 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
         <v>0</v>
@@ -765,7 +798,7 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C21" t="s">
         <v>0</v>
@@ -776,7 +809,7 @@
         <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C22" t="s">
         <v>0</v>
@@ -787,7 +820,7 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C23" t="s">
         <v>0</v>
@@ -798,7 +831,7 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C24" t="s">
         <v>0</v>
@@ -809,7 +842,7 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C25" t="s">
         <v>0</v>
@@ -817,10 +850,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C26" t="s">
         <v>0</v>
@@ -828,10 +861,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C27" t="s">
         <v>0</v>
@@ -842,7 +875,7 @@
         <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28" t="s">
         <v>0</v>
@@ -853,7 +886,7 @@
         <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" t="s">
         <v>0</v>
@@ -864,7 +897,7 @@
         <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" t="s">
         <v>0</v>
@@ -875,7 +908,7 @@
         <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C31" t="s">
         <v>0</v>
@@ -886,7 +919,7 @@
         <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C32" t="s">
         <v>0</v>
@@ -894,10 +927,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C33" t="s">
         <v>0</v>
@@ -908,7 +941,7 @@
         <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C34" t="s">
         <v>0</v>
@@ -933,7 +966,7 @@
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -944,12 +977,12 @@
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B38" t="s">
         <v>2</v>
@@ -960,10 +993,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C39" t="s">
         <v>0</v>
@@ -974,7 +1007,7 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C40" t="s">
         <v>0</v>
@@ -993,7 +1026,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B42" t="s">
         <v>2</v>
@@ -1004,7 +1037,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B43" t="s">
         <v>2</v>
@@ -1015,7 +1048,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B44" t="s">
         <v>2</v>
@@ -1032,7 +1065,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1059,13 +1092,13 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B48" t="s">
         <v>3</v>
       </c>
       <c r="C48" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1076,6 +1109,721 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>5</v>
+      </c>
+      <c r="B50" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>31</v>
+      </c>
+      <c r="B51" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>31</v>
+      </c>
+      <c r="B52" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>32</v>
+      </c>
+      <c r="B55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>14</v>
+      </c>
+      <c r="B56" t="s">
+        <v>15</v>
+      </c>
+      <c r="C56" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>14</v>
+      </c>
+      <c r="B57" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>14</v>
+      </c>
+      <c r="B58" t="s">
+        <v>15</v>
+      </c>
+      <c r="C58" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B59" t="s">
+        <v>15</v>
+      </c>
+      <c r="C59" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>14</v>
+      </c>
+      <c r="B60" t="s">
+        <v>15</v>
+      </c>
+      <c r="C60" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>14</v>
+      </c>
+      <c r="B61" t="s">
+        <v>15</v>
+      </c>
+      <c r="C61" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>14</v>
+      </c>
+      <c r="B62" t="s">
+        <v>15</v>
+      </c>
+      <c r="C62" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>14</v>
+      </c>
+      <c r="B63" t="s">
+        <v>15</v>
+      </c>
+      <c r="C63" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>14</v>
+      </c>
+      <c r="B64" t="s">
+        <v>15</v>
+      </c>
+      <c r="C64" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>14</v>
+      </c>
+      <c r="B65" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>14</v>
+      </c>
+      <c r="B66" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>14</v>
+      </c>
+      <c r="B67" t="s">
+        <v>15</v>
+      </c>
+      <c r="C67" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>14</v>
+      </c>
+      <c r="B68" t="s">
+        <v>15</v>
+      </c>
+      <c r="C68" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>14</v>
+      </c>
+      <c r="B69" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>14</v>
+      </c>
+      <c r="B70" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>14</v>
+      </c>
+      <c r="B71" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>14</v>
+      </c>
+      <c r="B72" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>14</v>
+      </c>
+      <c r="B73" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>14</v>
+      </c>
+      <c r="B74" t="s">
+        <v>15</v>
+      </c>
+      <c r="C74" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>14</v>
+      </c>
+      <c r="B75" t="s">
+        <v>15</v>
+      </c>
+      <c r="C75" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>14</v>
+      </c>
+      <c r="B76" t="s">
+        <v>15</v>
+      </c>
+      <c r="C76" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>14</v>
+      </c>
+      <c r="B77" t="s">
+        <v>15</v>
+      </c>
+      <c r="C77" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>14</v>
+      </c>
+      <c r="B78" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>14</v>
+      </c>
+      <c r="B79" t="s">
+        <v>15</v>
+      </c>
+      <c r="C79" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>14</v>
+      </c>
+      <c r="B80" t="s">
+        <v>15</v>
+      </c>
+      <c r="C80" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>14</v>
+      </c>
+      <c r="B81" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>14</v>
+      </c>
+      <c r="B82" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>14</v>
+      </c>
+      <c r="B83" t="s">
+        <v>15</v>
+      </c>
+      <c r="C83" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>14</v>
+      </c>
+      <c r="B84" t="s">
+        <v>15</v>
+      </c>
+      <c r="C84" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>14</v>
+      </c>
+      <c r="B85" t="s">
+        <v>15</v>
+      </c>
+      <c r="C85" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>11</v>
+      </c>
+      <c r="B86" t="s">
+        <v>15</v>
+      </c>
+      <c r="C86" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>11</v>
+      </c>
+      <c r="B87" t="s">
+        <v>15</v>
+      </c>
+      <c r="C87" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>33</v>
+      </c>
+      <c r="B88" t="s">
+        <v>15</v>
+      </c>
+      <c r="C88" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>34</v>
+      </c>
+      <c r="B89" t="s">
+        <v>15</v>
+      </c>
+      <c r="C89" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>35</v>
+      </c>
+      <c r="B90" t="s">
+        <v>15</v>
+      </c>
+      <c r="C90" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>36</v>
+      </c>
+      <c r="B91" t="s">
+        <v>15</v>
+      </c>
+      <c r="C91" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>36</v>
+      </c>
+      <c r="B92" t="s">
+        <v>15</v>
+      </c>
+      <c r="C92" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>37</v>
+      </c>
+      <c r="B93" t="s">
+        <v>15</v>
+      </c>
+      <c r="C93" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>36</v>
+      </c>
+      <c r="B94" t="s">
+        <v>15</v>
+      </c>
+      <c r="C94" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>6</v>
+      </c>
+      <c r="B95" t="s">
+        <v>15</v>
+      </c>
+      <c r="C95" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>33</v>
+      </c>
+      <c r="B96" t="s">
+        <v>15</v>
+      </c>
+      <c r="C96" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>33</v>
+      </c>
+      <c r="B97" t="s">
+        <v>15</v>
+      </c>
+      <c r="C97" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>33</v>
+      </c>
+      <c r="B98" t="s">
+        <v>15</v>
+      </c>
+      <c r="C98" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>33</v>
+      </c>
+      <c r="B99" t="s">
+        <v>15</v>
+      </c>
+      <c r="C99" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>33</v>
+      </c>
+      <c r="B100" t="s">
+        <v>38</v>
+      </c>
+      <c r="C100" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>33</v>
+      </c>
+      <c r="B101" t="s">
+        <v>15</v>
+      </c>
+      <c r="C101" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>33</v>
+      </c>
+      <c r="B102" t="s">
+        <v>15</v>
+      </c>
+      <c r="C102" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>40</v>
+      </c>
+      <c r="B103" t="s">
+        <v>38</v>
+      </c>
+      <c r="C103" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>33</v>
+      </c>
+      <c r="B104" t="s">
+        <v>15</v>
+      </c>
+      <c r="C104" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>33</v>
+      </c>
+      <c r="B105" t="s">
+        <v>38</v>
+      </c>
+      <c r="C105" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>33</v>
+      </c>
+      <c r="B106" t="s">
+        <v>15</v>
+      </c>
+      <c r="C106" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>41</v>
+      </c>
+      <c r="B107" t="s">
+        <v>15</v>
+      </c>
+      <c r="C107" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>33</v>
+      </c>
+      <c r="B108" t="s">
+        <v>38</v>
+      </c>
+      <c r="C108" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>6</v>
+      </c>
+      <c r="B109" t="s">
+        <v>2</v>
+      </c>
+      <c r="C109" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>6</v>
+      </c>
+      <c r="B110" t="s">
+        <v>2</v>
+      </c>
+      <c r="C110" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>13</v>
+      </c>
+      <c r="B111" t="s">
+        <v>2</v>
+      </c>
+      <c r="C111" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>42</v>
+      </c>
+      <c r="B112" t="s">
+        <v>15</v>
+      </c>
+      <c r="C112" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>14</v>
+      </c>
+      <c r="B113" t="s">
+        <v>15</v>
+      </c>
+      <c r="C113" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>14</v>
+      </c>
+      <c r="B114" t="s">
+        <v>38</v>
+      </c>
+      <c r="C114" t="s">
         <v>0</v>
       </c>
     </row>

--- a/Fishing.xlsx
+++ b/Fishing.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seeva\PycharmProjects\FishingAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51DC483-ACB0-45EB-8D4C-21FCA83C2331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD96960C-1F4D-4351-B43D-5B454E81B994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{82173828-75BE-405C-8870-0257E5D1189B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="58">
   <si>
     <t>Squid</t>
   </si>
@@ -137,9 +137,6 @@
     <t>Dusky kob</t>
   </si>
   <si>
-    <t>Russels Snapper</t>
-  </si>
-  <si>
     <t>Yellow edged pufferfish</t>
   </si>
   <si>
@@ -149,22 +146,70 @@
     <t>Blacktail</t>
   </si>
   <si>
-    <t>Backtail</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mid </t>
   </si>
   <si>
     <t>Earthworm lure</t>
   </si>
   <si>
-    <t xml:space="preserve">Russels Snapper </t>
-  </si>
-  <si>
     <t>Cape Moony</t>
   </si>
   <si>
     <t>Prison Goby</t>
+  </si>
+  <si>
+    <t>White Spotted Pufferfish</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cape Stumpnose</t>
+  </si>
+  <si>
+    <t>River Bream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dory Snapper </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low </t>
+  </si>
+  <si>
+    <t>Blue Lagoon</t>
+  </si>
+  <si>
+    <t>Durban Harbour</t>
+  </si>
+  <si>
+    <t>Shad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High </t>
+  </si>
+  <si>
+    <t>Lure</t>
+  </si>
+  <si>
+    <t>High outgoing tide</t>
+  </si>
+  <si>
+    <t>high tide outgoing</t>
+  </si>
+  <si>
+    <t>Very Low</t>
+  </si>
+  <si>
+    <t>Dusky Kob</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Durban harbour</t>
+  </si>
+  <si>
+    <t>Blue lagoon</t>
   </si>
 </sst>
 </file>
@@ -226,15 +271,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2393E883-3052-420D-BBA0-FE3DDC8041F9}" name="Table2" displayName="Table2" ref="A1:C114" totalsRowShown="0">
-  <autoFilter ref="A1:C114" xr:uid="{2393E883-3052-420D-BBA0-FE3DDC8041F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2393E883-3052-420D-BBA0-FE3DDC8041F9}" name="Table2" displayName="Table2" ref="A1:D248" totalsRowShown="0">
+  <autoFilter ref="A1:D248" xr:uid="{2393E883-3052-420D-BBA0-FE3DDC8041F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C18">
     <sortCondition ref="A1:A18"/>
   </sortState>
-  <tableColumns count="3">
+  <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{4F9A6E85-9E0A-45AB-9FCC-012B1D8EB2A3}" name="Fish"/>
     <tableColumn id="2" xr3:uid="{F65A0E92-79DD-4ED0-9CFA-94C2B26E8680}" name="Tidal_Coeff"/>
     <tableColumn id="3" xr3:uid="{C4386698-F65C-4503-A8B4-00615DD95A2B}" name="Bait_Used"/>
+    <tableColumn id="4" xr3:uid="{57320D19-ECA0-4645-B7ED-2223D001379D}" name="Location"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -557,23 +603,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{107E5C92-4114-4EFB-8BD8-377966D9CC54}">
-  <dimension ref="A1:C114"/>
+  <dimension ref="A1:J248"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
     <col min="2" max="2" width="19.7109375" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
-    <col min="4" max="4" width="25.5703125" customWidth="1"/>
-    <col min="5" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="30" customWidth="1"/>
-    <col min="13" max="13" width="15.28515625" customWidth="1"/>
-    <col min="14" max="14" width="19.7109375" customWidth="1"/>
+    <col min="3" max="4" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="25.5703125" customWidth="1"/>
+    <col min="6" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30" customWidth="1"/>
+    <col min="14" max="14" width="15.28515625" customWidth="1"/>
+    <col min="15" max="15" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -583,8 +629,14 @@
       <c r="C1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -594,8 +646,11 @@
       <c r="C2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -605,8 +660,11 @@
       <c r="C3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -616,8 +674,11 @@
       <c r="C4" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -627,8 +688,11 @@
       <c r="C5" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -638,8 +702,11 @@
       <c r="C6" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -649,8 +716,11 @@
       <c r="C7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -660,8 +730,11 @@
       <c r="C8" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -671,8 +744,11 @@
       <c r="C9" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -682,8 +758,11 @@
       <c r="C10" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -693,8 +772,11 @@
       <c r="C11" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -704,8 +786,11 @@
       <c r="C12" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -715,8 +800,11 @@
       <c r="C13" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -726,8 +814,11 @@
       <c r="C14" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -737,8 +828,11 @@
       <c r="C15" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -748,8 +842,11 @@
       <c r="C16" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -759,8 +856,11 @@
       <c r="C17" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -770,8 +870,11 @@
       <c r="C18" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -781,8 +884,11 @@
       <c r="C19" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -792,8 +898,11 @@
       <c r="C20" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -803,8 +912,11 @@
       <c r="C21" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -814,8 +926,11 @@
       <c r="C22" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -825,8 +940,11 @@
       <c r="C23" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -836,8 +954,11 @@
       <c r="C24" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -847,8 +968,11 @@
       <c r="C25" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -858,8 +982,11 @@
       <c r="C26" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -869,8 +996,11 @@
       <c r="C27" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>13</v>
       </c>
@@ -880,8 +1010,11 @@
       <c r="C28" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -891,8 +1024,11 @@
       <c r="C29" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -902,8 +1038,11 @@
       <c r="C30" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>13</v>
       </c>
@@ -913,8 +1052,11 @@
       <c r="C31" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -924,8 +1066,11 @@
       <c r="C32" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -935,8 +1080,11 @@
       <c r="C33" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -946,8 +1094,11 @@
       <c r="C34" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>12</v>
       </c>
@@ -957,8 +1108,11 @@
       <c r="C35" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -968,8 +1122,11 @@
       <c r="C36" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>10</v>
       </c>
@@ -979,8 +1136,11 @@
       <c r="C37" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>23</v>
       </c>
@@ -990,8 +1150,11 @@
       <c r="C38" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>24</v>
       </c>
@@ -1001,8 +1164,11 @@
       <c r="C39" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -1012,8 +1178,11 @@
       <c r="C40" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -1023,8 +1192,11 @@
       <c r="C41" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>25</v>
       </c>
@@ -1034,8 +1206,11 @@
       <c r="C42" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>26</v>
       </c>
@@ -1045,8 +1220,11 @@
       <c r="C43" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>27</v>
       </c>
@@ -1056,8 +1234,11 @@
       <c r="C44" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -1067,8 +1248,11 @@
       <c r="C45" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -1078,8 +1262,11 @@
       <c r="C46" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>5</v>
       </c>
@@ -1089,8 +1276,11 @@
       <c r="C47" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -1100,8 +1290,11 @@
       <c r="C48" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>5</v>
       </c>
@@ -1111,8 +1304,11 @@
       <c r="C49" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -1122,8 +1318,11 @@
       <c r="C50" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D50" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>31</v>
       </c>
@@ -1133,8 +1332,11 @@
       <c r="C51" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D51" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>31</v>
       </c>
@@ -1144,8 +1346,11 @@
       <c r="C52" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D52" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -1155,8 +1360,11 @@
       <c r="C53" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D53" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>6</v>
       </c>
@@ -1166,8 +1374,11 @@
       <c r="C54" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D54" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>32</v>
       </c>
@@ -1177,8 +1388,14 @@
       <c r="C55" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D55" t="s">
+        <v>57</v>
+      </c>
+      <c r="J55" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>14</v>
       </c>
@@ -1188,8 +1405,11 @@
       <c r="C56" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D56" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>14</v>
       </c>
@@ -1199,8 +1419,11 @@
       <c r="C57" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D57" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>14</v>
       </c>
@@ -1210,8 +1433,11 @@
       <c r="C58" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D58" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>14</v>
       </c>
@@ -1221,8 +1447,11 @@
       <c r="C59" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D59" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>14</v>
       </c>
@@ -1232,8 +1461,11 @@
       <c r="C60" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D60" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>14</v>
       </c>
@@ -1243,8 +1475,11 @@
       <c r="C61" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D61" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>14</v>
       </c>
@@ -1254,8 +1489,11 @@
       <c r="C62" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D62" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>14</v>
       </c>
@@ -1265,8 +1503,11 @@
       <c r="C63" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D63" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>14</v>
       </c>
@@ -1276,8 +1517,11 @@
       <c r="C64" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D64" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>14</v>
       </c>
@@ -1287,8 +1531,11 @@
       <c r="C65" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D65" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>14</v>
       </c>
@@ -1298,8 +1545,11 @@
       <c r="C66" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D66" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>14</v>
       </c>
@@ -1309,8 +1559,11 @@
       <c r="C67" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D67" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>14</v>
       </c>
@@ -1320,8 +1573,11 @@
       <c r="C68" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D68" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>14</v>
       </c>
@@ -1331,8 +1587,11 @@
       <c r="C69" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D69" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>14</v>
       </c>
@@ -1342,8 +1601,11 @@
       <c r="C70" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D70" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>14</v>
       </c>
@@ -1353,8 +1615,11 @@
       <c r="C71" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D71" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>14</v>
       </c>
@@ -1364,8 +1629,11 @@
       <c r="C72" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D72" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>14</v>
       </c>
@@ -1375,8 +1643,11 @@
       <c r="C73" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D73" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>14</v>
       </c>
@@ -1386,8 +1657,11 @@
       <c r="C74" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D74" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>14</v>
       </c>
@@ -1397,8 +1671,11 @@
       <c r="C75" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D75" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>14</v>
       </c>
@@ -1408,8 +1685,11 @@
       <c r="C76" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D76" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>14</v>
       </c>
@@ -1419,8 +1699,11 @@
       <c r="C77" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D77" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>14</v>
       </c>
@@ -1430,8 +1713,11 @@
       <c r="C78" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D78" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>14</v>
       </c>
@@ -1441,8 +1727,11 @@
       <c r="C79" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D79" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>14</v>
       </c>
@@ -1452,8 +1741,11 @@
       <c r="C80" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D80" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>14</v>
       </c>
@@ -1463,8 +1755,11 @@
       <c r="C81" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D81" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>14</v>
       </c>
@@ -1474,8 +1769,11 @@
       <c r="C82" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D82" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>14</v>
       </c>
@@ -1485,8 +1783,11 @@
       <c r="C83" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D83" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>14</v>
       </c>
@@ -1496,8 +1797,11 @@
       <c r="C84" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D84" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>14</v>
       </c>
@@ -1507,10 +1811,13 @@
       <c r="C85" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D85" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B86" t="s">
         <v>15</v>
@@ -1518,10 +1825,16 @@
       <c r="C86" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D86" t="s">
+        <v>56</v>
+      </c>
+      <c r="J86" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B87" t="s">
         <v>15</v>
@@ -1529,10 +1842,13 @@
       <c r="C87" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D87" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B88" t="s">
         <v>15</v>
@@ -1540,21 +1856,27 @@
       <c r="C88" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D88" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>33</v>
+      </c>
+      <c r="B89" t="s">
+        <v>15</v>
+      </c>
+      <c r="C89" t="s">
+        <v>0</v>
+      </c>
+      <c r="D89" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>34</v>
-      </c>
-      <c r="B89" t="s">
-        <v>15</v>
-      </c>
-      <c r="C89" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>35</v>
       </c>
       <c r="B90" t="s">
         <v>15</v>
@@ -1562,10 +1884,13 @@
       <c r="C90" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D90" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B91" t="s">
         <v>15</v>
@@ -1573,10 +1898,13 @@
       <c r="C91" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D91" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B92" t="s">
         <v>15</v>
@@ -1584,10 +1912,13 @@
       <c r="C92" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D92" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B93" t="s">
         <v>15</v>
@@ -1595,10 +1926,13 @@
       <c r="C93" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D93" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B94" t="s">
         <v>15</v>
@@ -1606,8 +1940,11 @@
       <c r="C94" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D94" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>6</v>
       </c>
@@ -1617,10 +1954,13 @@
       <c r="C95" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D95" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B96" t="s">
         <v>15</v>
@@ -1628,10 +1968,13 @@
       <c r="C96" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D96" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B97" t="s">
         <v>15</v>
@@ -1639,10 +1982,13 @@
       <c r="C97" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D97" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B98" t="s">
         <v>15</v>
@@ -1650,10 +1996,13 @@
       <c r="C98" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D98" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B99" t="s">
         <v>15</v>
@@ -1661,107 +2010,137 @@
       <c r="C99" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D99" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B100" t="s">
+        <v>36</v>
+      </c>
+      <c r="C100" t="s">
+        <v>0</v>
+      </c>
+      <c r="D100" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>26</v>
+      </c>
+      <c r="B101" t="s">
+        <v>15</v>
+      </c>
+      <c r="C101" t="s">
+        <v>0</v>
+      </c>
+      <c r="D101" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>26</v>
+      </c>
+      <c r="B102" t="s">
+        <v>15</v>
+      </c>
+      <c r="C102" t="s">
+        <v>37</v>
+      </c>
+      <c r="D102" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>44</v>
+      </c>
+      <c r="B103" t="s">
+        <v>36</v>
+      </c>
+      <c r="C103" t="s">
+        <v>0</v>
+      </c>
+      <c r="D103" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>26</v>
+      </c>
+      <c r="B104" t="s">
+        <v>15</v>
+      </c>
+      <c r="C104" t="s">
+        <v>0</v>
+      </c>
+      <c r="D104" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>26</v>
+      </c>
+      <c r="B105" t="s">
+        <v>36</v>
+      </c>
+      <c r="C105" t="s">
+        <v>0</v>
+      </c>
+      <c r="D105" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>26</v>
+      </c>
+      <c r="B106" t="s">
+        <v>15</v>
+      </c>
+      <c r="C106" t="s">
+        <v>0</v>
+      </c>
+      <c r="D106" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
         <v>38</v>
       </c>
-      <c r="C100" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>33</v>
-      </c>
-      <c r="B101" t="s">
-        <v>15</v>
-      </c>
-      <c r="C101" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>33</v>
-      </c>
-      <c r="B102" t="s">
-        <v>15</v>
-      </c>
-      <c r="C102" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>40</v>
-      </c>
-      <c r="B103" t="s">
-        <v>38</v>
-      </c>
-      <c r="C103" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>33</v>
-      </c>
-      <c r="B104" t="s">
-        <v>15</v>
-      </c>
-      <c r="C104" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>33</v>
-      </c>
-      <c r="B105" t="s">
-        <v>38</v>
-      </c>
-      <c r="C105" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>33</v>
-      </c>
-      <c r="B106" t="s">
-        <v>15</v>
-      </c>
-      <c r="C106" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>41</v>
-      </c>
       <c r="B107" t="s">
         <v>15</v>
       </c>
       <c r="C107" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D107" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B108" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C108" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D108" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>6</v>
       </c>
@@ -1771,8 +2150,11 @@
       <c r="C109" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D109" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>6</v>
       </c>
@@ -1782,8 +2164,11 @@
       <c r="C110" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D110" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>13</v>
       </c>
@@ -1793,38 +2178,1935 @@
       <c r="C111" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D111" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>39</v>
+      </c>
+      <c r="B112" t="s">
+        <v>15</v>
+      </c>
+      <c r="C112" t="s">
+        <v>0</v>
+      </c>
+      <c r="D112" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>14</v>
+      </c>
+      <c r="B113" t="s">
+        <v>15</v>
+      </c>
+      <c r="C113" t="s">
+        <v>0</v>
+      </c>
+      <c r="D113" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>14</v>
+      </c>
+      <c r="B114" t="s">
+        <v>36</v>
+      </c>
+      <c r="C114" t="s">
+        <v>0</v>
+      </c>
+      <c r="D114" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>26</v>
+      </c>
+      <c r="B115" t="s">
+        <v>15</v>
+      </c>
+      <c r="C115" t="s">
+        <v>0</v>
+      </c>
+      <c r="D115" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>26</v>
+      </c>
+      <c r="B116" t="s">
+        <v>36</v>
+      </c>
+      <c r="C116" t="s">
+        <v>0</v>
+      </c>
+      <c r="D116" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>26</v>
+      </c>
+      <c r="B117" t="s">
+        <v>15</v>
+      </c>
+      <c r="C117" t="s">
+        <v>0</v>
+      </c>
+      <c r="D117" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>26</v>
+      </c>
+      <c r="B118" t="s">
+        <v>15</v>
+      </c>
+      <c r="C118" t="s">
+        <v>0</v>
+      </c>
+      <c r="D118" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>40</v>
+      </c>
+      <c r="B119" t="s">
+        <v>15</v>
+      </c>
+      <c r="C119" t="s">
+        <v>0</v>
+      </c>
+      <c r="D119" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>35</v>
+      </c>
+      <c r="B120" t="s">
+        <v>15</v>
+      </c>
+      <c r="C120" t="s">
+        <v>0</v>
+      </c>
+      <c r="D120" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>35</v>
+      </c>
+      <c r="B121" t="s">
+        <v>15</v>
+      </c>
+      <c r="C121" t="s">
+        <v>0</v>
+      </c>
+      <c r="D121" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>35</v>
+      </c>
+      <c r="B122" t="s">
+        <v>15</v>
+      </c>
+      <c r="C122" t="s">
+        <v>41</v>
+      </c>
+      <c r="D122" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>6</v>
+      </c>
+      <c r="B123" t="s">
+        <v>15</v>
+      </c>
+      <c r="C123" t="s">
+        <v>0</v>
+      </c>
+      <c r="D123" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>6</v>
+      </c>
+      <c r="B124" t="s">
+        <v>15</v>
+      </c>
+      <c r="C124" t="s">
+        <v>0</v>
+      </c>
+      <c r="D124" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
         <v>42</v>
       </c>
-      <c r="B112" t="s">
-        <v>15</v>
-      </c>
-      <c r="C112" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>14</v>
-      </c>
-      <c r="B113" t="s">
-        <v>15</v>
-      </c>
-      <c r="C113" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>14</v>
-      </c>
-      <c r="B114" t="s">
+      <c r="B125" t="s">
+        <v>15</v>
+      </c>
+      <c r="C125" t="s">
+        <v>0</v>
+      </c>
+      <c r="D125" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>6</v>
+      </c>
+      <c r="B126" t="s">
+        <v>15</v>
+      </c>
+      <c r="C126" t="s">
+        <v>0</v>
+      </c>
+      <c r="D126" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>4</v>
+      </c>
+      <c r="B127" t="s">
+        <v>15</v>
+      </c>
+      <c r="C127" t="s">
+        <v>0</v>
+      </c>
+      <c r="D127" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>4</v>
+      </c>
+      <c r="B128" t="s">
+        <v>15</v>
+      </c>
+      <c r="C128" t="s">
+        <v>0</v>
+      </c>
+      <c r="D128" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>43</v>
+      </c>
+      <c r="B129" t="s">
+        <v>15</v>
+      </c>
+      <c r="C129" t="s">
+        <v>0</v>
+      </c>
+      <c r="D129" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>43</v>
+      </c>
+      <c r="B130" t="s">
+        <v>36</v>
+      </c>
+      <c r="C130" t="s">
+        <v>0</v>
+      </c>
+      <c r="D130" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>35</v>
+      </c>
+      <c r="B131" t="s">
+        <v>15</v>
+      </c>
+      <c r="C131" t="s">
+        <v>0</v>
+      </c>
+      <c r="D131" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>35</v>
+      </c>
+      <c r="B132" t="s">
+        <v>15</v>
+      </c>
+      <c r="C132" t="s">
+        <v>0</v>
+      </c>
+      <c r="D132" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>35</v>
+      </c>
+      <c r="B133" t="s">
+        <v>15</v>
+      </c>
+      <c r="C133" t="s">
+        <v>0</v>
+      </c>
+      <c r="D133" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>35</v>
+      </c>
+      <c r="B134" t="s">
+        <v>15</v>
+      </c>
+      <c r="C134" t="s">
+        <v>0</v>
+      </c>
+      <c r="D134" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>6</v>
+      </c>
+      <c r="B135" t="s">
+        <v>15</v>
+      </c>
+      <c r="C135" t="s">
+        <v>0</v>
+      </c>
+      <c r="D135" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>6</v>
+      </c>
+      <c r="B136" t="s">
+        <v>15</v>
+      </c>
+      <c r="C136" t="s">
+        <v>0</v>
+      </c>
+      <c r="D136" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>12</v>
+      </c>
+      <c r="B137" t="s">
+        <v>15</v>
+      </c>
+      <c r="C137" t="s">
+        <v>0</v>
+      </c>
+      <c r="D137" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>6</v>
+      </c>
+      <c r="B138" t="s">
+        <v>15</v>
+      </c>
+      <c r="C138" t="s">
+        <v>0</v>
+      </c>
+      <c r="D138" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
         <v>38</v>
       </c>
-      <c r="C114" t="s">
-        <v>0</v>
+      <c r="B139" t="s">
+        <v>15</v>
+      </c>
+      <c r="C139" t="s">
+        <v>0</v>
+      </c>
+      <c r="D139" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>38</v>
+      </c>
+      <c r="B140" t="s">
+        <v>36</v>
+      </c>
+      <c r="C140" t="s">
+        <v>0</v>
+      </c>
+      <c r="D140" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>17</v>
+      </c>
+      <c r="B141" t="s">
+        <v>36</v>
+      </c>
+      <c r="C141" t="s">
+        <v>0</v>
+      </c>
+      <c r="D141" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>5</v>
+      </c>
+      <c r="B142" t="s">
+        <v>15</v>
+      </c>
+      <c r="C142" t="s">
+        <v>0</v>
+      </c>
+      <c r="D142" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>5</v>
+      </c>
+      <c r="B143" t="s">
+        <v>15</v>
+      </c>
+      <c r="C143" t="s">
+        <v>0</v>
+      </c>
+      <c r="D143" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>35</v>
+      </c>
+      <c r="B144" t="s">
+        <v>15</v>
+      </c>
+      <c r="C144" t="s">
+        <v>0</v>
+      </c>
+      <c r="D144" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>5</v>
+      </c>
+      <c r="B145" t="s">
+        <v>2</v>
+      </c>
+      <c r="C145" t="s">
+        <v>0</v>
+      </c>
+      <c r="D145" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>17</v>
+      </c>
+      <c r="B146" t="s">
+        <v>2</v>
+      </c>
+      <c r="C146" t="s">
+        <v>0</v>
+      </c>
+      <c r="D146" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>26</v>
+      </c>
+      <c r="B147" t="s">
+        <v>2</v>
+      </c>
+      <c r="C147" t="s">
+        <v>0</v>
+      </c>
+      <c r="D147" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>26</v>
+      </c>
+      <c r="B148" t="s">
+        <v>2</v>
+      </c>
+      <c r="C148" t="s">
+        <v>0</v>
+      </c>
+      <c r="D148" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>26</v>
+      </c>
+      <c r="B149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C149" t="s">
+        <v>0</v>
+      </c>
+      <c r="D149" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>26</v>
+      </c>
+      <c r="B150" t="s">
+        <v>2</v>
+      </c>
+      <c r="C150" t="s">
+        <v>0</v>
+      </c>
+      <c r="D150" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>26</v>
+      </c>
+      <c r="B151" t="s">
+        <v>2</v>
+      </c>
+      <c r="C151" t="s">
+        <v>0</v>
+      </c>
+      <c r="D151" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>26</v>
+      </c>
+      <c r="B152" t="s">
+        <v>2</v>
+      </c>
+      <c r="C152" t="s">
+        <v>0</v>
+      </c>
+      <c r="D152" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>26</v>
+      </c>
+      <c r="B153" t="s">
+        <v>2</v>
+      </c>
+      <c r="C153" t="s">
+        <v>0</v>
+      </c>
+      <c r="D153" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>5</v>
+      </c>
+      <c r="B154" t="s">
+        <v>3</v>
+      </c>
+      <c r="C154" t="s">
+        <v>0</v>
+      </c>
+      <c r="D154" t="s">
+        <v>57</v>
+      </c>
+      <c r="J154" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>12</v>
+      </c>
+      <c r="B155" t="s">
+        <v>3</v>
+      </c>
+      <c r="C155" t="s">
+        <v>0</v>
+      </c>
+      <c r="D155" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>12</v>
+      </c>
+      <c r="B156" t="s">
+        <v>3</v>
+      </c>
+      <c r="C156" t="s">
+        <v>0</v>
+      </c>
+      <c r="D156" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>12</v>
+      </c>
+      <c r="B157" t="s">
+        <v>45</v>
+      </c>
+      <c r="C157" t="s">
+        <v>0</v>
+      </c>
+      <c r="D157" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>12</v>
+      </c>
+      <c r="B158" t="s">
+        <v>45</v>
+      </c>
+      <c r="C158" t="s">
+        <v>0</v>
+      </c>
+      <c r="D158" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>12</v>
+      </c>
+      <c r="B159" t="s">
+        <v>45</v>
+      </c>
+      <c r="C159" t="s">
+        <v>0</v>
+      </c>
+      <c r="D159" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>12</v>
+      </c>
+      <c r="B160" t="s">
+        <v>45</v>
+      </c>
+      <c r="C160" t="s">
+        <v>0</v>
+      </c>
+      <c r="D160" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>12</v>
+      </c>
+      <c r="B161" t="s">
+        <v>45</v>
+      </c>
+      <c r="C161" t="s">
+        <v>0</v>
+      </c>
+      <c r="D161" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>48</v>
+      </c>
+      <c r="B162" t="s">
+        <v>3</v>
+      </c>
+      <c r="C162" t="s">
+        <v>0</v>
+      </c>
+      <c r="D162" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>5</v>
+      </c>
+      <c r="B163" t="s">
+        <v>45</v>
+      </c>
+      <c r="C163" t="s">
+        <v>0</v>
+      </c>
+      <c r="D163" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>14</v>
+      </c>
+      <c r="B164" t="s">
+        <v>3</v>
+      </c>
+      <c r="C164" t="s">
+        <v>0</v>
+      </c>
+      <c r="D164" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>14</v>
+      </c>
+      <c r="B165" t="s">
+        <v>3</v>
+      </c>
+      <c r="C165" t="s">
+        <v>0</v>
+      </c>
+      <c r="D165" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>14</v>
+      </c>
+      <c r="B166" t="s">
+        <v>3</v>
+      </c>
+      <c r="C166" t="s">
+        <v>0</v>
+      </c>
+      <c r="D166" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>14</v>
+      </c>
+      <c r="B167" t="s">
+        <v>3</v>
+      </c>
+      <c r="C167" t="s">
+        <v>0</v>
+      </c>
+      <c r="D167" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>14</v>
+      </c>
+      <c r="B168" t="s">
+        <v>3</v>
+      </c>
+      <c r="C168" t="s">
+        <v>0</v>
+      </c>
+      <c r="D168" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>14</v>
+      </c>
+      <c r="B169" t="s">
+        <v>3</v>
+      </c>
+      <c r="C169" t="s">
+        <v>0</v>
+      </c>
+      <c r="D169" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>14</v>
+      </c>
+      <c r="B170" t="s">
+        <v>3</v>
+      </c>
+      <c r="C170" t="s">
+        <v>0</v>
+      </c>
+      <c r="D170" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>14</v>
+      </c>
+      <c r="B171" t="s">
+        <v>3</v>
+      </c>
+      <c r="C171" t="s">
+        <v>0</v>
+      </c>
+      <c r="D171" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>14</v>
+      </c>
+      <c r="B172" t="s">
+        <v>3</v>
+      </c>
+      <c r="C172" t="s">
+        <v>0</v>
+      </c>
+      <c r="D172" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>14</v>
+      </c>
+      <c r="B173" t="s">
+        <v>3</v>
+      </c>
+      <c r="C173" t="s">
+        <v>0</v>
+      </c>
+      <c r="D173" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>14</v>
+      </c>
+      <c r="B174" t="s">
+        <v>3</v>
+      </c>
+      <c r="C174" t="s">
+        <v>0</v>
+      </c>
+      <c r="D174" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>14</v>
+      </c>
+      <c r="B175" t="s">
+        <v>3</v>
+      </c>
+      <c r="C175" t="s">
+        <v>0</v>
+      </c>
+      <c r="D175" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>14</v>
+      </c>
+      <c r="B176" t="s">
+        <v>3</v>
+      </c>
+      <c r="C176" t="s">
+        <v>0</v>
+      </c>
+      <c r="D176" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>14</v>
+      </c>
+      <c r="B177" t="s">
+        <v>3</v>
+      </c>
+      <c r="C177" t="s">
+        <v>0</v>
+      </c>
+      <c r="D177" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>14</v>
+      </c>
+      <c r="B178" t="s">
+        <v>3</v>
+      </c>
+      <c r="C178" t="s">
+        <v>0</v>
+      </c>
+      <c r="D178" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>14</v>
+      </c>
+      <c r="B179" t="s">
+        <v>3</v>
+      </c>
+      <c r="C179" t="s">
+        <v>0</v>
+      </c>
+      <c r="D179" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>7</v>
+      </c>
+      <c r="B180" t="s">
+        <v>3</v>
+      </c>
+      <c r="C180" t="s">
+        <v>0</v>
+      </c>
+      <c r="D180" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>32</v>
+      </c>
+      <c r="B181" t="s">
+        <v>2</v>
+      </c>
+      <c r="C181" t="s">
+        <v>0</v>
+      </c>
+      <c r="D181" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>54</v>
+      </c>
+      <c r="B182" t="s">
+        <v>2</v>
+      </c>
+      <c r="C182" t="s">
+        <v>0</v>
+      </c>
+      <c r="D182" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>14</v>
+      </c>
+      <c r="B183" t="s">
+        <v>2</v>
+      </c>
+      <c r="C183" t="s">
+        <v>0</v>
+      </c>
+      <c r="D183" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>14</v>
+      </c>
+      <c r="B184" t="s">
+        <v>2</v>
+      </c>
+      <c r="C184" t="s">
+        <v>0</v>
+      </c>
+      <c r="D184" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>14</v>
+      </c>
+      <c r="B185" t="s">
+        <v>49</v>
+      </c>
+      <c r="C185" t="s">
+        <v>0</v>
+      </c>
+      <c r="D185" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>14</v>
+      </c>
+      <c r="B186" t="s">
+        <v>2</v>
+      </c>
+      <c r="C186" t="s">
+        <v>0</v>
+      </c>
+      <c r="D186" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>14</v>
+      </c>
+      <c r="B187" t="s">
+        <v>2</v>
+      </c>
+      <c r="C187" t="s">
+        <v>0</v>
+      </c>
+      <c r="D187" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>14</v>
+      </c>
+      <c r="B188" t="s">
+        <v>2</v>
+      </c>
+      <c r="C188" t="s">
+        <v>0</v>
+      </c>
+      <c r="D188" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>5</v>
+      </c>
+      <c r="B189" t="s">
+        <v>2</v>
+      </c>
+      <c r="C189" t="s">
+        <v>0</v>
+      </c>
+      <c r="D189" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>5</v>
+      </c>
+      <c r="B190" t="s">
+        <v>2</v>
+      </c>
+      <c r="C190" t="s">
+        <v>0</v>
+      </c>
+      <c r="D190" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>5</v>
+      </c>
+      <c r="B191" t="s">
+        <v>3</v>
+      </c>
+      <c r="C191" t="s">
+        <v>0</v>
+      </c>
+      <c r="D191" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>5</v>
+      </c>
+      <c r="B192" t="s">
+        <v>3</v>
+      </c>
+      <c r="C192" t="s">
+        <v>0</v>
+      </c>
+      <c r="D192" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>5</v>
+      </c>
+      <c r="B193" t="s">
+        <v>3</v>
+      </c>
+      <c r="C193" t="s">
+        <v>0</v>
+      </c>
+      <c r="D193" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>5</v>
+      </c>
+      <c r="B194" t="s">
+        <v>3</v>
+      </c>
+      <c r="C194" t="s">
+        <v>0</v>
+      </c>
+      <c r="D194" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>5</v>
+      </c>
+      <c r="B195" t="s">
+        <v>3</v>
+      </c>
+      <c r="C195" t="s">
+        <v>0</v>
+      </c>
+      <c r="D195" t="s">
+        <v>57</v>
+      </c>
+      <c r="G195" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>6</v>
+      </c>
+      <c r="B196" t="s">
+        <v>3</v>
+      </c>
+      <c r="C196" t="s">
+        <v>0</v>
+      </c>
+      <c r="D196" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>12</v>
+      </c>
+      <c r="B197" t="s">
+        <v>3</v>
+      </c>
+      <c r="C197" t="s">
+        <v>0</v>
+      </c>
+      <c r="D197" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>12</v>
+      </c>
+      <c r="B198" t="s">
+        <v>3</v>
+      </c>
+      <c r="C198" t="s">
+        <v>0</v>
+      </c>
+      <c r="D198" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>12</v>
+      </c>
+      <c r="B199" t="s">
+        <v>3</v>
+      </c>
+      <c r="C199" t="s">
+        <v>0</v>
+      </c>
+      <c r="D199" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>12</v>
+      </c>
+      <c r="B200" t="s">
+        <v>3</v>
+      </c>
+      <c r="C200" t="s">
+        <v>0</v>
+      </c>
+      <c r="D200" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>12</v>
+      </c>
+      <c r="B201" t="s">
+        <v>3</v>
+      </c>
+      <c r="C201" t="s">
+        <v>0</v>
+      </c>
+      <c r="D201" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>12</v>
+      </c>
+      <c r="B202" t="s">
+        <v>3</v>
+      </c>
+      <c r="C202" t="s">
+        <v>0</v>
+      </c>
+      <c r="D202" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>12</v>
+      </c>
+      <c r="B203" t="s">
+        <v>3</v>
+      </c>
+      <c r="C203" t="s">
+        <v>0</v>
+      </c>
+      <c r="D203" t="s">
+        <v>57</v>
+      </c>
+      <c r="G203" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>10</v>
+      </c>
+      <c r="B204" t="s">
+        <v>3</v>
+      </c>
+      <c r="C204" t="s">
+        <v>0</v>
+      </c>
+      <c r="D204" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>14</v>
+      </c>
+      <c r="B205" t="s">
+        <v>3</v>
+      </c>
+      <c r="C205" t="s">
+        <v>0</v>
+      </c>
+      <c r="D205" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>5</v>
+      </c>
+      <c r="B206" t="s">
+        <v>3</v>
+      </c>
+      <c r="C206" t="s">
+        <v>0</v>
+      </c>
+      <c r="D206" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>48</v>
+      </c>
+      <c r="B207" t="s">
+        <v>3</v>
+      </c>
+      <c r="C207" t="s">
+        <v>50</v>
+      </c>
+      <c r="D207" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>5</v>
+      </c>
+      <c r="B208" t="s">
+        <v>2</v>
+      </c>
+      <c r="C208" t="s">
+        <v>0</v>
+      </c>
+      <c r="D208" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>5</v>
+      </c>
+      <c r="B209" t="s">
+        <v>2</v>
+      </c>
+      <c r="C209" t="s">
+        <v>0</v>
+      </c>
+      <c r="D209" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>14</v>
+      </c>
+      <c r="B210" t="s">
+        <v>2</v>
+      </c>
+      <c r="C210" t="s">
+        <v>0</v>
+      </c>
+      <c r="D210" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>14</v>
+      </c>
+      <c r="B211" t="s">
+        <v>3</v>
+      </c>
+      <c r="C211" t="s">
+        <v>0</v>
+      </c>
+      <c r="D211" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>14</v>
+      </c>
+      <c r="B212" t="s">
+        <v>3</v>
+      </c>
+      <c r="C212" t="s">
+        <v>0</v>
+      </c>
+      <c r="D212" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>14</v>
+      </c>
+      <c r="B213" t="s">
+        <v>3</v>
+      </c>
+      <c r="C213" t="s">
+        <v>0</v>
+      </c>
+      <c r="D213" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>14</v>
+      </c>
+      <c r="B214" t="s">
+        <v>3</v>
+      </c>
+      <c r="C214" t="s">
+        <v>0</v>
+      </c>
+      <c r="D214" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>14</v>
+      </c>
+      <c r="B215" t="s">
+        <v>3</v>
+      </c>
+      <c r="C215" t="s">
+        <v>0</v>
+      </c>
+      <c r="D215" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>14</v>
+      </c>
+      <c r="B216" t="s">
+        <v>3</v>
+      </c>
+      <c r="C216" t="s">
+        <v>0</v>
+      </c>
+      <c r="D216" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>14</v>
+      </c>
+      <c r="B217" t="s">
+        <v>3</v>
+      </c>
+      <c r="C217" t="s">
+        <v>0</v>
+      </c>
+      <c r="D217" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>14</v>
+      </c>
+      <c r="B218" t="s">
+        <v>3</v>
+      </c>
+      <c r="C218" t="s">
+        <v>0</v>
+      </c>
+      <c r="D218" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>14</v>
+      </c>
+      <c r="B219" t="s">
+        <v>3</v>
+      </c>
+      <c r="C219" t="s">
+        <v>0</v>
+      </c>
+      <c r="D219" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>14</v>
+      </c>
+      <c r="B220" t="s">
+        <v>3</v>
+      </c>
+      <c r="C220" t="s">
+        <v>0</v>
+      </c>
+      <c r="D220" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>14</v>
+      </c>
+      <c r="B221" t="s">
+        <v>3</v>
+      </c>
+      <c r="C221" t="s">
+        <v>0</v>
+      </c>
+      <c r="D221" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>14</v>
+      </c>
+      <c r="B222" t="s">
+        <v>3</v>
+      </c>
+      <c r="C222" t="s">
+        <v>0</v>
+      </c>
+      <c r="D222" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>14</v>
+      </c>
+      <c r="B223" t="s">
+        <v>3</v>
+      </c>
+      <c r="C223" t="s">
+        <v>0</v>
+      </c>
+      <c r="D223" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>14</v>
+      </c>
+      <c r="B224" t="s">
+        <v>3</v>
+      </c>
+      <c r="C224" t="s">
+        <v>0</v>
+      </c>
+      <c r="D224" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>14</v>
+      </c>
+      <c r="B225" t="s">
+        <v>3</v>
+      </c>
+      <c r="C225" t="s">
+        <v>0</v>
+      </c>
+      <c r="D225" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>14</v>
+      </c>
+      <c r="B226" t="s">
+        <v>3</v>
+      </c>
+      <c r="C226" t="s">
+        <v>0</v>
+      </c>
+      <c r="D226" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>14</v>
+      </c>
+      <c r="B227" t="s">
+        <v>3</v>
+      </c>
+      <c r="C227" t="s">
+        <v>0</v>
+      </c>
+      <c r="D227" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>14</v>
+      </c>
+      <c r="B228" t="s">
+        <v>3</v>
+      </c>
+      <c r="C228" t="s">
+        <v>0</v>
+      </c>
+      <c r="D228" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>14</v>
+      </c>
+      <c r="B229" t="s">
+        <v>3</v>
+      </c>
+      <c r="C229" t="s">
+        <v>0</v>
+      </c>
+      <c r="D229" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>14</v>
+      </c>
+      <c r="B230" t="s">
+        <v>3</v>
+      </c>
+      <c r="C230" t="s">
+        <v>0</v>
+      </c>
+      <c r="D230" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>14</v>
+      </c>
+      <c r="B231" t="s">
+        <v>3</v>
+      </c>
+      <c r="C231" t="s">
+        <v>0</v>
+      </c>
+      <c r="D231" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>14</v>
+      </c>
+      <c r="B232" t="s">
+        <v>3</v>
+      </c>
+      <c r="C232" t="s">
+        <v>0</v>
+      </c>
+      <c r="D232" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>14</v>
+      </c>
+      <c r="B233" t="s">
+        <v>3</v>
+      </c>
+      <c r="C233" t="s">
+        <v>0</v>
+      </c>
+      <c r="D233" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>5</v>
+      </c>
+      <c r="B234" t="s">
+        <v>2</v>
+      </c>
+      <c r="C234" t="s">
+        <v>0</v>
+      </c>
+      <c r="D234" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>14</v>
+      </c>
+      <c r="B235" t="s">
+        <v>2</v>
+      </c>
+      <c r="C235" t="s">
+        <v>0</v>
+      </c>
+      <c r="D235" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>32</v>
+      </c>
+      <c r="B236" t="s">
+        <v>53</v>
+      </c>
+      <c r="C236" t="s">
+        <v>0</v>
+      </c>
+      <c r="D236" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>32</v>
+      </c>
+      <c r="B237" t="s">
+        <v>53</v>
+      </c>
+      <c r="C237" t="s">
+        <v>0</v>
+      </c>
+      <c r="D237" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>14</v>
+      </c>
+      <c r="B238" t="s">
+        <v>53</v>
+      </c>
+      <c r="C238" t="s">
+        <v>0</v>
+      </c>
+      <c r="D238" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>14</v>
+      </c>
+      <c r="B239" t="s">
+        <v>53</v>
+      </c>
+      <c r="C239" t="s">
+        <v>0</v>
+      </c>
+      <c r="D239" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>14</v>
+      </c>
+      <c r="B240" t="s">
+        <v>53</v>
+      </c>
+      <c r="C240" t="s">
+        <v>0</v>
+      </c>
+      <c r="D240" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>14</v>
+      </c>
+      <c r="B241" t="s">
+        <v>53</v>
+      </c>
+      <c r="C241" t="s">
+        <v>0</v>
+      </c>
+      <c r="D241" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>14</v>
+      </c>
+      <c r="B242" t="s">
+        <v>53</v>
+      </c>
+      <c r="C242" t="s">
+        <v>0</v>
+      </c>
+      <c r="D242" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>31</v>
+      </c>
+      <c r="B243" t="s">
+        <v>53</v>
+      </c>
+      <c r="C243" t="s">
+        <v>0</v>
+      </c>
+      <c r="D243" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>5</v>
+      </c>
+      <c r="B244" t="s">
+        <v>53</v>
+      </c>
+      <c r="C244" t="s">
+        <v>0</v>
+      </c>
+      <c r="D244" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>5</v>
+      </c>
+      <c r="B245" t="s">
+        <v>53</v>
+      </c>
+      <c r="C245" t="s">
+        <v>0</v>
+      </c>
+      <c r="D245" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>5</v>
+      </c>
+      <c r="B246" t="s">
+        <v>53</v>
+      </c>
+      <c r="C246" t="s">
+        <v>0</v>
+      </c>
+      <c r="D246" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>5</v>
+      </c>
+      <c r="B247" t="s">
+        <v>53</v>
+      </c>
+      <c r="C247" t="s">
+        <v>0</v>
+      </c>
+      <c r="D247" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>7</v>
+      </c>
+      <c r="B248" t="s">
+        <v>53</v>
+      </c>
+      <c r="C248" t="s">
+        <v>0</v>
+      </c>
+      <c r="D248" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
